--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:05:40+00:00</t>
+    <t>2026-06-24T16:17:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:17:55+00:00</t>
+    <t>2026-06-24T17:45:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T17:45:04+00:00</t>
+    <t>2026-06-25T07:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:04:27+00:00</t>
+    <t>2026-06-25T07:50:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:50:33+00:00</t>
+    <t>2026-06-25T07:55:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:55:44+00:00</t>
+    <t>2026-06-25T08:09:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T08:09:35+00:00</t>
+    <t>2026-06-25T08:24:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T08:24:45+00:00</t>
+    <t>2026-06-25T12:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T12:30:35+00:00</t>
+    <t>2026-06-25T12:40:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T12:40:37+00:00</t>
+    <t>2026-06-25T12:53:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T12:53:40+00:00</t>
+    <t>2026-06-26T08:03:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T08:03:05+00:00</t>
+    <t>2026-06-26T08:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T08:06:54+00:00</t>
+    <t>2026-07-14T09:00:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:00:12+00:00</t>
+    <t>2026-07-14T13:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T13:33:33+00:00</t>
+    <t>2026-07-14T13:42:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T13:42:28+00:00</t>
+    <t>2026-07-14T13:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T13:52:20+00:00</t>
+    <t>2026-07-14T14:06:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T14:06:40+00:00</t>
+    <t>2026-07-14T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.1</t>
   </si>
   <si>
     <t>Name</t>
